--- a/engine/publish_queue/ARCC/ARCC_Valuation_Model_09092026_public.xlsx
+++ b/engine/publish_queue/ARCC/ARCC_Valuation_Model_09092026_public.xlsx
@@ -5002,6 +5002,34 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Terminal useful life: the disclosed 20 years of machinery and equipment, the class the replacement-cost base actually represents (adopted), vs the longest life disclosed in the same accounting-policies note, 50 years</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20 years</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>50 years</t>
+        </is>
+      </c>
+      <c r="D23" s="10">
+        <f>DCF!$B$44</f>
+        <v/>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>82.59023265802607</v>
+      </c>
+      <c r="F23" s="8">
+        <f>E23/D23-1</f>
+        <v/>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
